--- a/state_fact_sheets/data/modified/il_rlps_ghgrp_naics_2023.xlsx
+++ b/state_fact_sheets/data/modified/il_rlps_ghgrp_naics_2023.xlsx
@@ -3171,7 +3171,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Other Manufacturing</t>
+          <t>Other Chemicals Manufacturing</t>
         </is>
       </c>
       <c r="D101">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Other Manufacturing</t>
+          <t>Other Chemicals Manufacturing</t>
         </is>
       </c>
       <c r="D125">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Other Manufacturing</t>
+          <t>Other Chemicals Manufacturing</t>
         </is>
       </c>
       <c r="D129">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Other Manufacturing</t>
+          <t>Other Chemicals Manufacturing</t>
         </is>
       </c>
       <c r="D130">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Other Manufacturing</t>
+          <t>Other Chemicals Manufacturing</t>
         </is>
       </c>
       <c r="D147">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Other Manufacturing</t>
+          <t>Other Chemicals Manufacturing</t>
         </is>
       </c>
       <c r="D193">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Other Manufacturing</t>
+          <t>Other Chemicals Manufacturing</t>
         </is>
       </c>
       <c r="D226">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Other Manufacturing</t>
+          <t>Other Chemicals Manufacturing</t>
         </is>
       </c>
       <c r="D265">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Other Manufacturing</t>
+          <t>Other Chemicals Manufacturing</t>
         </is>
       </c>
       <c r="D267">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Other Manufacturing</t>
+          <t>Other Chemicals Manufacturing</t>
         </is>
       </c>
       <c r="D268">
